--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -40,7 +40,7 @@
     <t>en.report.json</t>
   </si>
   <si>
-    <t>["hero-banner","hero-banner","cards-nav","columns-media","columns-media","cards-feature","cards-news","cards-event","cards-stats","carousel-stories"]</t>
+    <t>["hero-banner","hero-banner","cards-nav","columns-media","columns-media","columns-media","columns-media","cards-feature","cards-news","cards-event","cards-stats","carousel-stories"]</t>
   </si>
   <si>
     <t>en</t>
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-08-06T17:48:45.299Z</t>
+    <t>2026-08-06T18:44:40.253Z</t>
   </si>
   <si>
     <t>Atlas Copco Group Homepage</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-08-06T18:44:40.253Z</t>
+    <t>2026-08-07T18:32:10.377Z</t>
   </si>
   <si>
     <t>Atlas Copco Group Homepage</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-08-07T18:32:10.377Z</t>
+    <t>2026-08-10T13:52:01.469Z</t>
   </si>
   <si>
     <t>Atlas Copco Group Homepage</t>
